--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0001T0006Z000C1N71_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0001T0006Z000C1N71_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>59.18733280081789</v>
+        <v>9.617941580132907</v>
       </c>
       <c r="D2" t="n">
-        <v>60.21106557398161</v>
+        <v>9.784298155772012</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
